--- a/output/pdf_financials_xlsx/LWR.xlsx
+++ b/output/pdf_financials_xlsx/LWR.xlsx
@@ -5045,22 +5045,22 @@
         <v>1.244264</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.946278</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.946278</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.99523</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.220633</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.303596</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.313903</v>
       </c>
     </row>
     <row r="93">
@@ -8280,7 +8280,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10270,7 +10274,11 @@
           <t>Reserves (Note 8) 2,220,633</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11386,7 +11394,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -11726,7 +11738,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LWR.xlsx
+++ b/output/pdf_financials_xlsx/LWR.xlsx
@@ -939,25 +939,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1736,25 +1736,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.06631099999999999</v>
+        <v>-0.066313</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.779027</v>
+        <v>-0.779065</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.750355</v>
+        <v>-1.750425</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.432706</v>
+        <v>-0.432856</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.242196</v>
+        <v>-2.242199</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.998135</v>
+        <v>-2.998155</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.900865</v>
+        <v>-1.900872</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.587495</v>
@@ -1763,10 +1763,10 @@
         <v>-2.851433</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.071046</v>
+        <v>-1.071054</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.000667</v>
+        <v>-1.000692</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.428306</v>
@@ -1834,25 +1834,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.06631099999999999</v>
+        <v>-0.066313</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.779027</v>
+        <v>-0.779065</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.750355</v>
+        <v>-1.750425</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.432706</v>
+        <v>-0.432856</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.242196</v>
+        <v>-2.242199</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.998135</v>
+        <v>-2.998155</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.900865</v>
+        <v>-1.900872</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.587495</v>
@@ -1861,10 +1861,10 @@
         <v>-2.830265</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.03226</v>
+        <v>-1.032268</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.983049</v>
+        <v>-0.983074</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.424681</v>
@@ -2117,22 +2117,22 @@
         <v>0.027133</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.882953</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.086146</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.599237</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.066749</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.005032</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.003092</v>
       </c>
     </row>
     <row r="35">
@@ -2215,22 +2215,22 @@
         <v>0.027133</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.882953</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.086146</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.599237</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.066749</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.005032</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.003092</v>
       </c>
     </row>
     <row r="37">
@@ -2803,22 +2803,22 @@
         <v>0.005569</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.989528</v>
+        <v>0.106575</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.086146</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.660243</v>
+        <v>0.061006</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.097978</v>
+        <v>0.031229</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.050866</v>
+        <v>0.045834</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.005692</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="49">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -33394,7 +33394,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -38262,7 +38262,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -46794,7 +46794,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" s="5" t="n">

--- a/output/pdf_financials_xlsx/LWR.xlsx
+++ b/output/pdf_financials_xlsx/LWR.xlsx
@@ -697,25 +697,25 @@
         <v>0.027046</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.345916</v>
+        <v>0.367954</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.46294</v>
+        <v>0.501435</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.366452</v>
+        <v>0.369072</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.276978</v>
+        <v>0.279755</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.739933</v>
+        <v>0.760451</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.56075</v>
+        <v>0.5679419999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.283762</v>
+        <v>0.288701</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.761895</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.009095000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.103459</v>
+        <v>0.112554</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.034058</v>
@@ -2803,7 +2803,7 @@
         <v>0.005569</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.106575</v>
+        <v>0.09748</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -5917,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.115567</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.115567</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>-0.060211</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.627712</v>
+        <v>-0.743279</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.986269</v>
@@ -20058,7 +20058,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -27846,7 +27850,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -29316,7 +29324,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -37930,7 +37942,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
